--- a/testbuild/StructureDefinition-no-basis-person-citizenship.xlsx
+++ b/testbuild/StructureDefinition-no-basis-person-citizenship.xlsx
@@ -24,13 +24,13 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://hl7.no/fhir/ig/StructureDefinition/no-basis-person-citizenship</t>
+    <t>http://hl7.no/fhir/StructureDefinition/no-basis-person-citizenship</t>
   </si>
   <si>
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.3-test</t>
+    <t>2.2.4-test</t>
   </si>
   <si>
     <t>Name</t>
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>active</t>
+    <t>draft</t>
   </si>
   <si>
     <t>Experimental</t>
